--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/207.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/207.xlsx
@@ -426,13 +426,13 @@
         <v>-0.8544428093269353</v>
       </c>
       <c r="E2">
-        <v>-14.00938436479078</v>
+        <v>-14.86433761506891</v>
       </c>
       <c r="F2">
-        <v>-2.229737394548007</v>
+        <v>-3.038922293400884</v>
       </c>
       <c r="G2">
-        <v>-8.674630248311704</v>
+        <v>-7.657627348102056</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.215495815457294</v>
       </c>
       <c r="E3">
-        <v>-15.49657145670179</v>
+        <v>-15.36950700452057</v>
       </c>
       <c r="F3">
-        <v>-2.076335348693178</v>
+        <v>-3.544518822801771</v>
       </c>
       <c r="G3">
-        <v>-7.563286731869445</v>
+        <v>-8.342244855077798</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.59588641826586</v>
       </c>
       <c r="E4">
-        <v>-16.34205566782988</v>
+        <v>-15.28413168405396</v>
       </c>
       <c r="F4">
-        <v>-2.253622540240328</v>
+        <v>-3.054161768510187</v>
       </c>
       <c r="G4">
-        <v>-8.634734864017947</v>
+        <v>-7.769844910246731</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.941172333682964</v>
       </c>
       <c r="E5">
-        <v>-16.50590038590139</v>
+        <v>-17.04885083399905</v>
       </c>
       <c r="F5">
-        <v>-2.281057240253645</v>
+        <v>-3.082008167122695</v>
       </c>
       <c r="G5">
-        <v>-8.610614229218816</v>
+        <v>-8.053657979328451</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.241059683429117</v>
       </c>
       <c r="E6">
-        <v>-15.8041725821468</v>
+        <v>-18.60658702247555</v>
       </c>
       <c r="F6">
-        <v>-2.813111824499948</v>
+        <v>-2.956426012123484</v>
       </c>
       <c r="G6">
-        <v>-8.01804313041697</v>
+        <v>-7.419552776190907</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.470291582100542</v>
       </c>
       <c r="E7">
-        <v>-17.198784079919</v>
+        <v>-17.92237082770862</v>
       </c>
       <c r="F7">
-        <v>-2.534433291217541</v>
+        <v>-2.949187737757823</v>
       </c>
       <c r="G7">
-        <v>-8.455187426695574</v>
+        <v>-7.587562962308921</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.615361515939444</v>
       </c>
       <c r="E8">
-        <v>-19.85960219497592</v>
+        <v>-17.81692078196601</v>
       </c>
       <c r="F8">
-        <v>-2.232903414761507</v>
+        <v>-3.136808812654897</v>
       </c>
       <c r="G8">
-        <v>-8.188241587136442</v>
+        <v>-7.524980409434538</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.65978419150475</v>
       </c>
       <c r="E9">
-        <v>-19.25107491477319</v>
+        <v>-19.24246628568461</v>
       </c>
       <c r="F9">
-        <v>-2.345837227887372</v>
+        <v>-2.880137516162664</v>
       </c>
       <c r="G9">
-        <v>-7.859282608535682</v>
+        <v>-7.251761086078487</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.595875511526931</v>
       </c>
       <c r="E10">
-        <v>-19.55445097396905</v>
+        <v>-19.28546867486144</v>
       </c>
       <c r="F10">
-        <v>-2.185820668321188</v>
+        <v>-2.983248548626133</v>
       </c>
       <c r="G10">
-        <v>-7.655300034587948</v>
+        <v>-6.198974499134857</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.4196925444645</v>
       </c>
       <c r="E11">
-        <v>-20.32102652551348</v>
+        <v>-20.27786563974637</v>
       </c>
       <c r="F11">
-        <v>-2.260063925164497</v>
+        <v>-3.088196071621607</v>
       </c>
       <c r="G11">
-        <v>-6.52324243470647</v>
+        <v>-6.652631796563345</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.133073600376119</v>
       </c>
       <c r="E12">
-        <v>-19.58078857879766</v>
+        <v>-21.7947051794596</v>
       </c>
       <c r="F12">
-        <v>-2.780573552917983</v>
+        <v>-2.852362357146796</v>
       </c>
       <c r="G12">
-        <v>-6.095745068129302</v>
+        <v>-6.541642446813738</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.745927263071231</v>
       </c>
       <c r="E13">
-        <v>-22.7776919753566</v>
+        <v>-21.39827803635414</v>
       </c>
       <c r="F13">
-        <v>-2.177751541450518</v>
+        <v>-2.932694114400682</v>
       </c>
       <c r="G13">
-        <v>-5.493742225086073</v>
+        <v>-5.368712851704418</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.272172314995154</v>
       </c>
       <c r="E14">
-        <v>-20.56990240002703</v>
+        <v>-21.18557561221386</v>
       </c>
       <c r="F14">
-        <v>-2.320204226975144</v>
+        <v>-2.44121048044129</v>
       </c>
       <c r="G14">
-        <v>-4.801785238649766</v>
+        <v>-5.475799068263223</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.7248499730940863</v>
       </c>
       <c r="E15">
-        <v>-24.83564340272036</v>
+        <v>-22.75223742295948</v>
       </c>
       <c r="F15">
-        <v>-1.821807038671988</v>
+        <v>-2.493719033369945</v>
       </c>
       <c r="G15">
-        <v>-4.866830837405367</v>
+        <v>-4.26953890066452</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.1232539114092294</v>
       </c>
       <c r="E16">
-        <v>-22.63648509884942</v>
+        <v>-23.97522881278899</v>
       </c>
       <c r="F16">
-        <v>-1.738421919171384</v>
+        <v>-2.437033851996375</v>
       </c>
       <c r="G16">
-        <v>-4.64991727258124</v>
+        <v>-3.875084089114819</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.5172501543870747</v>
       </c>
       <c r="E17">
-        <v>-24.43999515714421</v>
+        <v>-24.59879062669718</v>
       </c>
       <c r="F17">
-        <v>-1.904637980380119</v>
+        <v>-2.784481790324391</v>
       </c>
       <c r="G17">
-        <v>-4.134518300845344</v>
+        <v>-3.638426430694479</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.182312437470643</v>
       </c>
       <c r="E18">
-        <v>-25.76484098435425</v>
+        <v>-25.26697149500295</v>
       </c>
       <c r="F18">
-        <v>-1.219052953331553</v>
+        <v>-2.558225659760748</v>
       </c>
       <c r="G18">
-        <v>-4.200649758537826</v>
+        <v>-3.846259169104385</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.851003825328299</v>
       </c>
       <c r="E19">
-        <v>-26.2152792369492</v>
+        <v>-25.88475044760335</v>
       </c>
       <c r="F19">
-        <v>-1.720500190411816</v>
+        <v>-2.116307389347865</v>
       </c>
       <c r="G19">
-        <v>-4.171745385434449</v>
+        <v>-4.015398251251288</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.504136484212699</v>
       </c>
       <c r="E20">
-        <v>-25.67866412398828</v>
+        <v>-26.18879672095235</v>
       </c>
       <c r="F20">
-        <v>-1.180073296825419</v>
+        <v>-1.858121837243315</v>
       </c>
       <c r="G20">
-        <v>-3.073193816955934</v>
+        <v>-2.773692072563609</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.118466172258395</v>
       </c>
       <c r="E21">
-        <v>-26.49032063427907</v>
+        <v>-26.73091845830659</v>
       </c>
       <c r="F21">
-        <v>-0.5997025270760294</v>
+        <v>-1.996688651281408</v>
       </c>
       <c r="G21">
-        <v>-2.987434134761114</v>
+        <v>-3.387414246815859</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.664100800691595</v>
       </c>
       <c r="E22">
-        <v>-27.44216511442531</v>
+        <v>-27.24667541998819</v>
       </c>
       <c r="F22">
-        <v>-0.6700400316151383</v>
+        <v>-1.746337798072536</v>
       </c>
       <c r="G22">
-        <v>-3.527370870034087</v>
+        <v>-3.530436435203452</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.115371488522348</v>
       </c>
       <c r="E23">
-        <v>-27.5536244451761</v>
+        <v>-27.51029600587071</v>
       </c>
       <c r="F23">
-        <v>-0.8734149977786533</v>
+        <v>-1.836491507621415</v>
       </c>
       <c r="G23">
-        <v>-3.6450541428641</v>
+        <v>-2.772536692170403</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.450591634925217</v>
       </c>
       <c r="E24">
-        <v>-26.14254741591201</v>
+        <v>-26.81285213852738</v>
       </c>
       <c r="F24">
-        <v>-0.380885135789526</v>
+        <v>-1.557590143507654</v>
       </c>
       <c r="G24">
-        <v>-2.038946285032222</v>
+        <v>-2.487300088506798</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.651453693269651</v>
       </c>
       <c r="E25">
-        <v>-27.57666532092713</v>
+        <v>-27.65625325161193</v>
       </c>
       <c r="F25">
-        <v>-0.5127587412129989</v>
+        <v>-1.327239392871974</v>
       </c>
       <c r="G25">
-        <v>-3.122683162222499</v>
+        <v>-2.336958283931875</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.706923704605384</v>
       </c>
       <c r="E26">
-        <v>-28.82033372307566</v>
+        <v>-28.14004824374739</v>
       </c>
       <c r="F26">
-        <v>-0.5456722632284317</v>
+        <v>-1.252549645998556</v>
       </c>
       <c r="G26">
-        <v>-2.592750895569203</v>
+        <v>-3.03719163421636</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.613930626583069</v>
       </c>
       <c r="E27">
-        <v>-29.36551218038509</v>
+        <v>-28.27620587173601</v>
       </c>
       <c r="F27">
-        <v>-0.4409376306554762</v>
+        <v>-1.316303286420215</v>
       </c>
       <c r="G27">
-        <v>-2.070095208011225</v>
+        <v>-2.657362812859159</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.377523014487811</v>
       </c>
       <c r="E28">
-        <v>-27.24203826260433</v>
+        <v>-28.01393477110777</v>
       </c>
       <c r="F28">
-        <v>-0.5134172932982245</v>
+        <v>-1.341027568291571</v>
       </c>
       <c r="G28">
-        <v>-3.091809014523256</v>
+        <v>-2.753027647307478</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.009940201445611</v>
       </c>
       <c r="E29">
-        <v>-28.71843400095506</v>
+        <v>-27.81318298987374</v>
       </c>
       <c r="F29">
-        <v>-0.8956260129499164</v>
+        <v>-1.265338810330378</v>
       </c>
       <c r="G29">
-        <v>-2.51068578219621</v>
+        <v>-2.861520845720474</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.529238128225221</v>
       </c>
       <c r="E30">
-        <v>-29.91976117113188</v>
+        <v>-27.07464774938481</v>
       </c>
       <c r="F30">
-        <v>-0.2011840816306181</v>
+        <v>-1.10378231576239</v>
       </c>
       <c r="G30">
-        <v>-4.008542111439458</v>
+        <v>-3.263361484368289</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.961117796411426</v>
       </c>
       <c r="E31">
-        <v>-29.25936474964529</v>
+        <v>-26.83398199824716</v>
       </c>
       <c r="F31">
-        <v>-0.2958349978092952</v>
+        <v>-1.227048355503373</v>
       </c>
       <c r="G31">
-        <v>-2.818265257704356</v>
+        <v>-2.541821462993055</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.335242696520245</v>
       </c>
       <c r="E32">
-        <v>-28.69760754899378</v>
+        <v>-27.52899860352239</v>
       </c>
       <c r="F32">
-        <v>-0.8496590774011691</v>
+        <v>-1.4593656503533</v>
       </c>
       <c r="G32">
-        <v>-1.925702453770373</v>
+        <v>-3.142420634727634</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.682194284958773</v>
       </c>
       <c r="E33">
-        <v>-28.11907235214386</v>
+        <v>-27.11078497196602</v>
       </c>
       <c r="F33">
-        <v>0.1226280495933199</v>
+        <v>-1.847932089821478</v>
       </c>
       <c r="G33">
-        <v>-2.196385899243342</v>
+        <v>-2.83568865887754</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.037236939839882</v>
       </c>
       <c r="E34">
-        <v>-26.88452429664677</v>
+        <v>-25.46045507545468</v>
       </c>
       <c r="F34">
-        <v>-0.9193264327114131</v>
+        <v>-1.185369877998919</v>
       </c>
       <c r="G34">
-        <v>-3.47857342878523</v>
+        <v>-3.182488167389433</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.430088410954625</v>
       </c>
       <c r="E35">
-        <v>-27.33238131905735</v>
+        <v>-25.92600937428723</v>
       </c>
       <c r="F35">
-        <v>-0.02983794109634594</v>
+        <v>-1.354214348976737</v>
       </c>
       <c r="G35">
-        <v>-3.851112428864956</v>
+        <v>-3.38863252757431</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.1154620021049255</v>
       </c>
       <c r="E36">
-        <v>-24.9663759188478</v>
+        <v>-26.25176062355499</v>
       </c>
       <c r="F36">
-        <v>-0.3480279427574837</v>
+        <v>-0.9795561982015624</v>
       </c>
       <c r="G36">
-        <v>-3.217119784275749</v>
+        <v>-4.419950226695767</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.5751711165899176</v>
       </c>
       <c r="E37">
-        <v>-26.49358113556459</v>
+        <v>-24.74880991362329</v>
       </c>
       <c r="F37">
-        <v>-0.08113542088210812</v>
+        <v>-1.247865228335725</v>
       </c>
       <c r="G37">
-        <v>-3.926963648260737</v>
+        <v>-4.297125676643267</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.936229842303596</v>
       </c>
       <c r="E38">
-        <v>-24.75684342651289</v>
+        <v>-25.62248387544912</v>
       </c>
       <c r="F38">
-        <v>0.4835121071947441</v>
+        <v>-0.9177467360742744</v>
       </c>
       <c r="G38">
-        <v>-5.037353727587687</v>
+        <v>-4.334405729960999</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.194176245864253</v>
       </c>
       <c r="E39">
-        <v>-24.81800499646049</v>
+        <v>-24.12521187192303</v>
       </c>
       <c r="F39">
-        <v>-0.3751950800996962</v>
+        <v>-0.8924740749822643</v>
       </c>
       <c r="G39">
-        <v>-3.918074833487794</v>
+        <v>-4.837098827917172</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.34610222285991</v>
       </c>
       <c r="E40">
-        <v>-24.80711854494605</v>
+        <v>-23.45596681222546</v>
       </c>
       <c r="F40">
-        <v>-0.3395719683097063</v>
+        <v>-1.133283792445692</v>
       </c>
       <c r="G40">
-        <v>-4.156215616309728</v>
+        <v>-4.800470952070675</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.400380050247525</v>
       </c>
       <c r="E41">
-        <v>-22.46962441708879</v>
+        <v>-22.50834739832838</v>
       </c>
       <c r="F41">
-        <v>-0.1955147351258583</v>
+        <v>-1.04561767020742</v>
       </c>
       <c r="G41">
-        <v>-5.313274456103783</v>
+        <v>-4.621161874027131</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.370101871112795</v>
       </c>
       <c r="E42">
-        <v>-22.74314424715208</v>
+        <v>-22.83216498919486</v>
       </c>
       <c r="F42">
-        <v>-0.5047442865909137</v>
+        <v>-1.029326996863965</v>
       </c>
       <c r="G42">
-        <v>-4.399590371629249</v>
+        <v>-4.326774922492979</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.270097754401831</v>
       </c>
       <c r="E43">
-        <v>-22.80812784916215</v>
+        <v>-21.79188846862683</v>
       </c>
       <c r="F43">
-        <v>-0.9158348641086131</v>
+        <v>-0.8665304362939866</v>
       </c>
       <c r="G43">
-        <v>-4.95507342875464</v>
+        <v>-5.275305809313881</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.120964212864863</v>
       </c>
       <c r="E44">
-        <v>-22.54930744572776</v>
+        <v>-21.09819870623586</v>
       </c>
       <c r="F44">
-        <v>-0.03257238189298711</v>
+        <v>-0.9049501164358277</v>
       </c>
       <c r="G44">
-        <v>-5.334352699552323</v>
+        <v>-4.877212708216521</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.9433374736760562</v>
       </c>
       <c r="E45">
-        <v>-21.5838186733964</v>
+        <v>-20.73165949158101</v>
       </c>
       <c r="F45">
-        <v>0.5149643891116386</v>
+        <v>-0.5218169387626115</v>
       </c>
       <c r="G45">
-        <v>-3.888912237832355</v>
+        <v>-5.308603276347871</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.7577876684833311</v>
       </c>
       <c r="E46">
-        <v>-21.24657415709718</v>
+        <v>-19.54065271366768</v>
       </c>
       <c r="F46">
-        <v>0.3833583463592699</v>
+        <v>-0.7136775980272134</v>
       </c>
       <c r="G46">
-        <v>-4.472763359683761</v>
+        <v>-4.679738666798995</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.5834558647686602</v>
       </c>
       <c r="E47">
-        <v>-19.58639482961916</v>
+        <v>-18.72939470908956</v>
       </c>
       <c r="F47">
-        <v>0.521766942223428</v>
+        <v>-0.5232856341677751</v>
       </c>
       <c r="G47">
-        <v>-4.092755768867439</v>
+        <v>-5.566713269862689</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.4353788042912322</v>
       </c>
       <c r="E48">
-        <v>-19.60642427015508</v>
+        <v>-18.76322240992686</v>
       </c>
       <c r="F48">
-        <v>0.3513518866499026</v>
+        <v>-0.8531440190647466</v>
       </c>
       <c r="G48">
-        <v>-6.026048152891026</v>
+        <v>-5.977992273842966</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.3261107288317698</v>
       </c>
       <c r="E49">
-        <v>-19.66344681485967</v>
+        <v>-17.35645648791807</v>
       </c>
       <c r="F49">
-        <v>0.3786482493069518</v>
+        <v>-0.6342876945103116</v>
       </c>
       <c r="G49">
-        <v>-4.293398002366048</v>
+        <v>-5.534938653776764</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.2620811742607224</v>
       </c>
       <c r="E50">
-        <v>-16.33222435075922</v>
+        <v>-17.83488070988043</v>
       </c>
       <c r="F50">
-        <v>0.3580194158750358</v>
+        <v>-0.6838331772391528</v>
       </c>
       <c r="G50">
-        <v>-4.647745554707478</v>
+        <v>-6.038267376476476</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.2451539999660845</v>
       </c>
       <c r="E51">
-        <v>-18.38774851605488</v>
+        <v>-16.86868549560388</v>
       </c>
       <c r="F51">
-        <v>-0.03210683941261379</v>
+        <v>-0.7796860545192921</v>
       </c>
       <c r="G51">
-        <v>-5.544999401670609</v>
+        <v>-6.361472626929983</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.2754213010078186</v>
       </c>
       <c r="E52">
-        <v>-15.50390305612021</v>
+        <v>-16.72981078321066</v>
       </c>
       <c r="F52">
-        <v>0.4809731611051636</v>
+        <v>-0.5617848375802849</v>
       </c>
       <c r="G52">
-        <v>-5.530826956216988</v>
+        <v>-5.858402126782333</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.3477543793068769</v>
       </c>
       <c r="E53">
-        <v>-16.60601136078897</v>
+        <v>-14.37611830382796</v>
       </c>
       <c r="F53">
-        <v>0.1209986509120132</v>
+        <v>-0.6048011284402603</v>
       </c>
       <c r="G53">
-        <v>-5.908043757143705</v>
+        <v>-5.572543140557345</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.4559567260335123</v>
       </c>
       <c r="E54">
-        <v>-16.45567960915633</v>
+        <v>-15.66616280828904</v>
       </c>
       <c r="F54">
-        <v>0.6265338811250927</v>
+        <v>-0.8357615574844017</v>
       </c>
       <c r="G54">
-        <v>-5.864748442581116</v>
+        <v>-6.272630826838101</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.5947660315333556</v>
       </c>
       <c r="E55">
-        <v>-14.93726868896244</v>
+        <v>-15.5668941295669</v>
       </c>
       <c r="F55">
-        <v>0.6290554314992144</v>
+        <v>-0.8425475432481353</v>
       </c>
       <c r="G55">
-        <v>-5.806651678912446</v>
+        <v>-7.559655063412865</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.7561312257942948</v>
       </c>
       <c r="E56">
-        <v>-15.36522759658332</v>
+        <v>-13.88366939786384</v>
       </c>
       <c r="F56">
-        <v>0.3855029895651177</v>
+        <v>-0.8951513584281123</v>
       </c>
       <c r="G56">
-        <v>-7.273279632083749</v>
+        <v>-7.049586069995196</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.9336087680781004</v>
       </c>
       <c r="E57">
-        <v>-15.71027920207177</v>
+        <v>-13.99592121156598</v>
       </c>
       <c r="F57">
-        <v>0.620029540278311</v>
+        <v>-0.6739830604524639</v>
       </c>
       <c r="G57">
-        <v>-7.738662881812336</v>
+        <v>-7.484677828039451</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.123370032527664</v>
       </c>
       <c r="E58">
-        <v>-13.38534706111178</v>
+        <v>-13.94969907736968</v>
       </c>
       <c r="F58">
-        <v>0.1302250070443941</v>
+        <v>-0.4313351957222243</v>
       </c>
       <c r="G58">
-        <v>-6.890630225927089</v>
+        <v>-7.123338403519079</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.319909884977144</v>
       </c>
       <c r="E59">
-        <v>-13.94064212935434</v>
+        <v>-13.15568097333877</v>
       </c>
       <c r="F59">
-        <v>0.3238774250012513</v>
+        <v>-0.7809194935820605</v>
       </c>
       <c r="G59">
-        <v>-7.691318770055219</v>
+        <v>-7.887299755434534</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.52014496141493</v>
       </c>
       <c r="E60">
-        <v>-13.10741649736502</v>
+        <v>-11.99943476190832</v>
       </c>
       <c r="F60">
-        <v>0.4320431553566024</v>
+        <v>-0.4513999109528339</v>
       </c>
       <c r="G60">
-        <v>-7.551150271922476</v>
+        <v>-8.02481319604478</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.723129877086931</v>
       </c>
       <c r="E61">
-        <v>-12.42325917276019</v>
+        <v>-12.12388175611311</v>
       </c>
       <c r="F61">
-        <v>-0.03405350280919263</v>
+        <v>-0.6750508260346725</v>
       </c>
       <c r="G61">
-        <v>-6.949081217968462</v>
+        <v>-8.210859234260743</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.924934074257824</v>
       </c>
       <c r="E62">
-        <v>-12.76984140246324</v>
+        <v>-10.5467772843058</v>
       </c>
       <c r="F62">
-        <v>0.5944951150870162</v>
+        <v>-0.565134755357206</v>
       </c>
       <c r="G62">
-        <v>-7.290295836155604</v>
+        <v>-8.225604404092657</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.124321931170559</v>
       </c>
       <c r="E63">
-        <v>-12.92316194694093</v>
+        <v>-11.29831377367075</v>
       </c>
       <c r="F63">
-        <v>0.02917495267909084</v>
+        <v>-0.900350192248082</v>
       </c>
       <c r="G63">
-        <v>-7.241091197805416</v>
+        <v>-7.742019774989157</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.320325138839147</v>
       </c>
       <c r="E64">
-        <v>-12.28154057869015</v>
+        <v>-10.70529198847029</v>
       </c>
       <c r="F64">
-        <v>0.307310905312664</v>
+        <v>-0.999885162633665</v>
       </c>
       <c r="G64">
-        <v>-7.395243440296039</v>
+        <v>-7.982474629143042</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.507420806603499</v>
       </c>
       <c r="E65">
-        <v>-12.24007787067592</v>
+        <v>-11.25950927989903</v>
       </c>
       <c r="F65">
-        <v>-0.3831590043102107</v>
+        <v>-0.6344997565654282</v>
       </c>
       <c r="G65">
-        <v>-8.483356858689232</v>
+        <v>-8.721838627701711</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.683026543851931</v>
       </c>
       <c r="E66">
-        <v>-11.94494363417402</v>
+        <v>-11.95075366632586</v>
       </c>
       <c r="F66">
-        <v>-0.3795970244781728</v>
+        <v>-0.9742778411109239</v>
       </c>
       <c r="G66">
-        <v>-7.431311833946399</v>
+        <v>-7.998676439012234</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.842780135342499</v>
       </c>
       <c r="E67">
-        <v>-10.89784723175044</v>
+        <v>-9.963111326405178</v>
       </c>
       <c r="F67">
-        <v>-0.3522973483515123</v>
+        <v>-1.230346914501321</v>
       </c>
       <c r="G67">
-        <v>-8.500959029321537</v>
+        <v>-8.252049041860355</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.979384095792169</v>
       </c>
       <c r="E68">
-        <v>-11.93736296868518</v>
+        <v>-9.785894024589007</v>
       </c>
       <c r="F68">
-        <v>-0.3851686236294023</v>
+        <v>-1.271377608696786</v>
       </c>
       <c r="G68">
-        <v>-8.158463230010698</v>
+        <v>-8.47028351435465</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.092046145936981</v>
       </c>
       <c r="E69">
-        <v>-12.46515208580515</v>
+        <v>-11.10226254845668</v>
       </c>
       <c r="F69">
-        <v>-0.5024381117415199</v>
+        <v>-0.7924222033373344</v>
       </c>
       <c r="G69">
-        <v>-7.234340995450842</v>
+        <v>-8.403850797018096</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.178656488806463</v>
       </c>
       <c r="E70">
-        <v>-11.23353395299103</v>
+        <v>-10.6297298711783</v>
       </c>
       <c r="F70">
-        <v>-0.1482215833652289</v>
+        <v>-1.213399345807446</v>
       </c>
       <c r="G70">
-        <v>-8.621522476770716</v>
+        <v>-8.316919181702374</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.235246532412637</v>
       </c>
       <c r="E71">
-        <v>-12.368238213567</v>
+        <v>-10.35517302056726</v>
       </c>
       <c r="F71">
-        <v>-0.6479118531841551</v>
+        <v>-1.206110541030213</v>
       </c>
       <c r="G71">
-        <v>-9.910417171575167</v>
+        <v>-8.104362294807927</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.261436201573229</v>
       </c>
       <c r="E72">
-        <v>-12.46013906507866</v>
+        <v>-10.57156615102378</v>
       </c>
       <c r="F72">
-        <v>-0.4055042150007274</v>
+        <v>-1.832186482229065</v>
       </c>
       <c r="G72">
-        <v>-7.388178736115234</v>
+        <v>-7.761022306384573</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.253775160386413</v>
       </c>
       <c r="E73">
-        <v>-12.00598746379741</v>
+        <v>-9.679425072194668</v>
       </c>
       <c r="F73">
-        <v>-0.7587001947367693</v>
+        <v>-1.864898710965618</v>
       </c>
       <c r="G73">
-        <v>-6.82113194342117</v>
+        <v>-7.561641390736427</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.209268785609122</v>
       </c>
       <c r="E74">
-        <v>-12.16447499711786</v>
+        <v>-11.07096626458967</v>
       </c>
       <c r="F74">
-        <v>-0.7877063077131968</v>
+        <v>-1.891465281940801</v>
       </c>
       <c r="G74">
-        <v>-7.90803039160145</v>
+        <v>-7.026157339213773</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.127335194360757</v>
       </c>
       <c r="E75">
-        <v>-12.74955836738288</v>
+        <v>-10.5293064315842</v>
       </c>
       <c r="F75">
-        <v>-0.9747781750222148</v>
+        <v>-2.048408598442598</v>
       </c>
       <c r="G75">
-        <v>-6.919269755387324</v>
+        <v>-7.545816983058711</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.004842331298049</v>
       </c>
       <c r="E76">
-        <v>-12.79234338980735</v>
+        <v>-11.29918776915423</v>
       </c>
       <c r="F76">
-        <v>-0.3207348935700455</v>
+        <v>-1.710917636296232</v>
       </c>
       <c r="G76">
-        <v>-7.442984817517869</v>
+        <v>-7.674120485978705</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.841287547631923</v>
       </c>
       <c r="E77">
-        <v>-13.2398879475114</v>
+        <v>-12.65328753845382</v>
       </c>
       <c r="F77">
-        <v>-1.029573850349999</v>
+        <v>-2.002039904703493</v>
       </c>
       <c r="G77">
-        <v>-6.271995202094561</v>
+        <v>-7.383441345448538</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.637510124061499</v>
       </c>
       <c r="E78">
-        <v>-14.00273203647351</v>
+        <v>-12.51429508573639</v>
       </c>
       <c r="F78">
-        <v>-1.076619320257192</v>
+        <v>-2.179011488270176</v>
       </c>
       <c r="G78">
-        <v>-6.34295674572884</v>
+        <v>-6.139944161624112</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.39352893047898</v>
       </c>
       <c r="E79">
-        <v>-15.22145307531379</v>
+        <v>-14.05406681782446</v>
       </c>
       <c r="F79">
-        <v>-2.0221037915667</v>
+        <v>-2.299825560498873</v>
       </c>
       <c r="G79">
-        <v>-5.7047464661226</v>
+        <v>-6.445149975980602</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.114769837046583</v>
       </c>
       <c r="E80">
-        <v>-14.03039648418637</v>
+        <v>-14.33465559581373</v>
       </c>
       <c r="F80">
-        <v>-1.45801623985414</v>
+        <v>-2.31047090999225</v>
       </c>
       <c r="G80">
-        <v>-4.907007618069962</v>
+        <v>-6.33564044008705</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.807273661290846</v>
       </c>
       <c r="E81">
-        <v>-15.79094038109639</v>
+        <v>-13.98695483303079</v>
       </c>
       <c r="F81">
-        <v>-1.424607354131833</v>
+        <v>-1.975302690043333</v>
       </c>
       <c r="G81">
-        <v>-6.126241813637069</v>
+        <v>-6.105120533096518</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.477156859523202</v>
       </c>
       <c r="E82">
-        <v>-17.68888723634715</v>
+        <v>-14.80318510206932</v>
       </c>
       <c r="F82">
-        <v>-1.384769508996399</v>
+        <v>-1.906525829691099</v>
       </c>
       <c r="G82">
-        <v>-5.610445576436461</v>
+        <v>-5.334895629020763</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.135937263342331</v>
       </c>
       <c r="E83">
-        <v>-17.40231181571974</v>
+        <v>-16.08021477223237</v>
       </c>
       <c r="F83">
-        <v>-1.43125831600891</v>
+        <v>-2.657512119925491</v>
       </c>
       <c r="G83">
-        <v>-5.462454259194421</v>
+        <v>-4.995932181800325</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.7935490993850438</v>
       </c>
       <c r="E84">
-        <v>-19.23113604371742</v>
+        <v>-17.65932988649908</v>
       </c>
       <c r="F84">
-        <v>-1.558940382374218</v>
+        <v>-2.647167467799331</v>
       </c>
       <c r="G84">
-        <v>-4.862020614736806</v>
+        <v>-4.698052604722243</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.4589081126483555</v>
       </c>
       <c r="E85">
-        <v>-19.06702414567944</v>
+        <v>-18.30010895858444</v>
       </c>
       <c r="F85">
-        <v>-1.819127270123931</v>
+        <v>-2.715906223251037</v>
       </c>
       <c r="G85">
-        <v>-4.25150635911211</v>
+        <v>-4.355957381421655</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.1448846016149251</v>
       </c>
       <c r="E86">
-        <v>-20.71267160006685</v>
+        <v>-19.75113618554419</v>
       </c>
       <c r="F86">
-        <v>-1.792144858712543</v>
+        <v>-3.070526994919894</v>
       </c>
       <c r="G86">
-        <v>-4.505464928520681</v>
+        <v>-4.805592366019928</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.1386113696159876</v>
       </c>
       <c r="E87">
-        <v>-20.69682194104</v>
+        <v>-19.7766450796294</v>
       </c>
       <c r="F87">
-        <v>-2.032829492698148</v>
+        <v>-3.372812342447281</v>
       </c>
       <c r="G87">
-        <v>-3.776876755692339</v>
+        <v>-4.446573633922586</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.3834441295815099</v>
       </c>
       <c r="E88">
-        <v>-23.50343427677386</v>
+        <v>-21.5934371521887</v>
       </c>
       <c r="F88">
-        <v>-2.444012018997558</v>
+        <v>-3.11664137986634</v>
       </c>
       <c r="G88">
-        <v>-4.148028637191111</v>
+        <v>-3.581782996517549</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.577372753934535</v>
       </c>
       <c r="E89">
-        <v>-24.47004611065912</v>
+        <v>-22.46529519593745</v>
       </c>
       <c r="F89">
-        <v>-2.382932348552136</v>
+        <v>-3.446181671680636</v>
       </c>
       <c r="G89">
-        <v>-3.585007467872799</v>
+        <v>-4.018328084053544</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.7112594041602879</v>
       </c>
       <c r="E90">
-        <v>-24.3474150345314</v>
+        <v>-24.9785348715584</v>
       </c>
       <c r="F90">
-        <v>-2.132911185569578</v>
+        <v>-3.58635551848016</v>
       </c>
       <c r="G90">
-        <v>-3.945274275638446</v>
+        <v>-3.421125532042257</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.7794331140409499</v>
       </c>
       <c r="E91">
-        <v>-28.52928869860268</v>
+        <v>-25.38174566872736</v>
       </c>
       <c r="F91">
-        <v>-2.103212557444411</v>
+        <v>-3.865486340364495</v>
       </c>
       <c r="G91">
-        <v>-3.713400355522353</v>
+        <v>-3.764319856461883</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.7735821232785398</v>
       </c>
       <c r="E92">
-        <v>-29.12352864331121</v>
+        <v>-27.30241187807459</v>
       </c>
       <c r="F92">
-        <v>-2.66155372448375</v>
+        <v>-4.266724315993297</v>
       </c>
       <c r="G92">
-        <v>-4.076792318277072</v>
+        <v>-3.786103246110288</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.6892944213850121</v>
       </c>
       <c r="E93">
-        <v>-30.39160099188708</v>
+        <v>-28.67467082814493</v>
       </c>
       <c r="F93">
-        <v>-3.588423951884951</v>
+        <v>-4.153677016533249</v>
       </c>
       <c r="G93">
-        <v>-3.857554750484378</v>
+        <v>-3.842160713726767</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.527582777705089</v>
       </c>
       <c r="E94">
-        <v>-32.44725195445496</v>
+        <v>-30.99131812590788</v>
       </c>
       <c r="F94">
-        <v>-3.475838881435664</v>
+        <v>-4.518296182753897</v>
       </c>
       <c r="G94">
-        <v>-3.227958510371323</v>
+        <v>-3.772506835580501</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.2886561545591849</v>
       </c>
       <c r="E95">
-        <v>-34.94783454522446</v>
+        <v>-33.81303518669433</v>
       </c>
       <c r="F95">
-        <v>-3.626069936872577</v>
+        <v>-4.666211951299984</v>
       </c>
       <c r="G95">
-        <v>-3.490306002176407</v>
+        <v>-3.859319271256809</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.02782031214537707</v>
       </c>
       <c r="E96">
-        <v>-36.42161056136175</v>
+        <v>-36.11627140868357</v>
       </c>
       <c r="F96">
-        <v>-3.327852701660338</v>
+        <v>-4.926320144146432</v>
       </c>
       <c r="G96">
-        <v>-5.135167106090993</v>
+        <v>-4.695483621383769</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.406346460908204</v>
       </c>
       <c r="E97">
-        <v>-39.2331159132609</v>
+        <v>-37.081221292608</v>
       </c>
       <c r="F97">
-        <v>-3.923076098941923</v>
+        <v>-4.885177620351589</v>
       </c>
       <c r="G97">
-        <v>-5.205589030802369</v>
+        <v>-4.871435806250493</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.8532681023259305</v>
       </c>
       <c r="E98">
-        <v>-43.00291429229321</v>
+        <v>-39.70342737403851</v>
       </c>
       <c r="F98">
-        <v>-4.470064490725895</v>
+        <v>-5.032813400715531</v>
       </c>
       <c r="G98">
-        <v>-5.07890107410554</v>
+        <v>-5.59963664525074</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.340921873675023</v>
       </c>
       <c r="E99">
-        <v>-43.69476323000006</v>
+        <v>-40.88827769153842</v>
       </c>
       <c r="F99">
-        <v>-4.435482636761225</v>
+        <v>-5.455338761861475</v>
       </c>
       <c r="G99">
-        <v>-5.32264329997992</v>
+        <v>-5.195660704730095</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.887574824026639</v>
       </c>
       <c r="E100">
-        <v>-46.18924370204423</v>
+        <v>-44.19533168985993</v>
       </c>
       <c r="F100">
-        <v>-4.362588790417076</v>
+        <v>-6.136613793313275</v>
       </c>
       <c r="G100">
-        <v>-6.157496674073328</v>
+        <v>-6.871177460338332</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.437695130922217</v>
       </c>
       <c r="E101">
-        <v>-48.57544496420949</v>
+        <v>-45.47274628031362</v>
       </c>
       <c r="F101">
-        <v>-4.260176900041571</v>
+        <v>-5.804801289713099</v>
       </c>
       <c r="G101">
-        <v>-5.91842231740932</v>
+        <v>-6.851317497648244</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.062861864652036</v>
       </c>
       <c r="E102">
-        <v>-49.45179298993686</v>
+        <v>-47.800864202738</v>
       </c>
       <c r="F102">
-        <v>-4.637042649945205</v>
+        <v>-5.885276354527669</v>
       </c>
       <c r="G102">
-        <v>-5.79591226918305</v>
+        <v>-6.919173749566686</v>
       </c>
     </row>
   </sheetData>
